--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:19</t>
+    <t xml:space="preserve">2026-09-29 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:09</t>
+    <t xml:space="preserve">2026-09-29 18:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -555,7 +555,7 @@
         <v>-8.67</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>36.11</v>
+        <v>36.1</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>44.77</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:46</t>
+    <t xml:space="preserve">2026-10-05 04:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -513,7 +513,7 @@
         <v>7.1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>71.41</v>
+        <v>71.42</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>64.32</v>
@@ -555,10 +555,10 @@
         <v>-8.67</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>36.1</v>
+        <v>36.11</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>44.77</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="7">
